--- a/outputs/evaluation/architecture/validation/CF_M09/run_1/CF_M09_arch_eval_llm_report.xlsx
+++ b/outputs/evaluation/architecture/validation/CF_M09/run_1/CF_M09_arch_eval_llm_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,12 +544,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Service that performs all the important logic of the platform and communicates with the data layer.</t>
+          <t>This is the service that performs all the important logic of the platform.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -581,55 +581,59 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AU_14</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>HTTP</t>
-        </is>
-      </c>
+          <t>AU_18</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Connector</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Communication protocol used between client and server.</t>
+          <t>This is the service that performs all the important logic of the platform. It is the service that has communication with the data layer.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AU_16</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>AU_07, AU_05</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>functional service, data layer</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CF_M09_AU38</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>CF_M09_AU19</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Business layer (Backend)</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Therefore, controllers are responsible for receiving HTTP requests and forwarding them to the providers.</t>
+          <t xml:space="preserve">The business layer is divided into two services hosted on different machines. </t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.7066</v>
+        <v>0.772</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AU_16</t>
+          <t>AU_19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -640,290 +644,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>La comunicaci´ on entre ambos se realiza a trav´ es de internet utilizando el modelo de REST API y el protocolo de comunicaci´ on HTTP.</t>
+          <t>For better response speed of the system, there is a user cache system stored in Amazon DynamoDB, to which the business service has access.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>AU_02, AU_03</t>
+          <t>AU_06, AU_13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>server, presentation layer</t>
+          <t>business service, amazon dynamodb</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CF_M09_AU07</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>CF_M09_AU27</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Amazon DynamoDB</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>On one side is the client, who makes the various requests, and on the other side is the server, who receives and processes them.</t>
+          <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.7314000000000001</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>AU_18</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Es el servicio que tiene comunicaci´ on con la capa de datos.</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>AU_07, AU_05</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>functional service, data layer</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>CF_M09_AU10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Data layer</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>This is the layer responsible for storing information.</t>
-        </is>
-      </c>
-      <c r="L6" t="n">
-        <v>0.7706</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>AU_19</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Connector</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Cache de usuarios: Para mejorar la velocidad de respuesta del sistema, existe un sistema de cach´ e de usuarios almacenada en Amazon DynamoDB, a la cu´ al tiene acceso el servicio business.</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>AU_06, AU_13</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>business service, amazon dynamodb</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>CF_M09_AU26</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>User Cache</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>To improve system response speed, there is a user cache system stored in Amazon DynamoDB</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>0.7848000000000001</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>P_02</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3-Layer Architecture</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Architectural Pattern</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>This architecture divides the system into three parts: the presentation layer, the business layer, and the data layer.</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>CF_M09_P02</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Three Layers</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>To decouple the components of the client-server model, a three-tier architecture has been used.</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>0.8511</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>P_04</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>MVC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Model-View-Controller design pattern.</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>P_03</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>CF_M09_AU11</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>View</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>This is the part responsible for displaying information to the user.</t>
-        </is>
-      </c>
-      <c r="L9" t="n">
-        <v>0.7269</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>P_07</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Module</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Design Pattern</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Allows encapsulating information and exposing only what is intended to be shared.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>CF_M09_AU35</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Modules</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Modules are classes that allow NestJS to organize the application.</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>0.9649</v>
+        <v>0.7688</v>
       </c>
     </row>
   </sheetData>
